--- a/AAII_Financials/Yearly/SBAC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SBAC_YR_FIN.xlsx
@@ -2273,7 +2273,7 @@
         <v>284500</v>
       </c>
       <c r="F43" s="3">
-        <v>201100</v>
+        <v>349200</v>
       </c>
       <c r="G43" s="3">
         <v>263900</v>
@@ -2426,7 +2426,7 @@
         <v>1724200</v>
       </c>
       <c r="F46" s="3">
-        <v>482200</v>
+        <v>630300</v>
       </c>
       <c r="G46" s="3">
         <v>481400</v>
@@ -2732,7 +2732,7 @@
         <v>522900</v>
       </c>
       <c r="F52" s="3">
-        <v>608100</v>
+        <v>460000</v>
       </c>
       <c r="G52" s="3">
         <v>474900</v>
@@ -4468,25 +4468,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1234800</v>
+        <v>-224800</v>
       </c>
       <c r="E91" s="3">
-        <v>-471800</v>
+        <v>-228100</v>
       </c>
       <c r="F91" s="3">
-        <v>-323400</v>
+        <v>-236700</v>
       </c>
       <c r="G91" s="3">
-        <v>-1306900</v>
+        <v>-214400</v>
       </c>
       <c r="H91" s="3">
-        <v>-408400</v>
+        <v>-133700</v>
       </c>
       <c r="I91" s="3">
-        <v>-310000</v>
+        <v>-128600</v>
       </c>
       <c r="J91" s="3">
-        <v>-855700</v>
+        <v>-154200</v>
       </c>
       <c r="K91" s="3">
         <v>-556500</v>
